--- a/data/trans_orig/P79A3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A3_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>68,11%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>18539</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>70,02%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>33223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
